--- a/www/download/COUNTRY.IDN.EXI382.xlsx
+++ b/www/download/COUNTRY.IDN.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>Indonésia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830613496933</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830613496933</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830613496933</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830613496933</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830613496933</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830613496933</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830613496933</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830613496933</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830613496933</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830613496933</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830613496933</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830613496933</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830613496933</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830858895706</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830858895706</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830858895706</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830858895706</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830858895706</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830858895706</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830858895706</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830858895706</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830858895706</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830858895706</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830858895706</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830858895706</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830858895706</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32830858895706</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>903.992</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>343.831</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>347.06</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>350.402</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>340.596</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>354.792</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>368.966</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>371.303</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>368.071</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>369.935</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>366.99</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>371.99</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>372.913</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>373.531</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>373.848</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>374.535</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>374.286</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>377.183</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>379.204</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>373.496</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>393.622</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>484.106</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>518.33</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>580.329</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>578.665</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>639.782</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>684.917</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>84.527</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>27.988</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>27.941</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>28.24</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>28.166</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>28.112</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>27.958</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>27.79</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>27.206</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>26.444</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>26.458</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>28.528</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>28.575</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>28.599</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>28.652</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>28.633</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>28.854</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>29.009</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>31.322</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>35.903</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>49.322</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>51.98</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>58.088</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>59.385</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>64.621</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>68.271</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2171833.039</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>818402.313</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>844057.515</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>843181.748</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>824584.604</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>851441.141</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>906000.225</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>899003.887</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>880933.995</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>894204.418</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>897202.015</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>896040.133</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>892578.846</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>894320.887</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>895341</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>897249.373</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>896914.317</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>904368.491</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>909727.741</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>895207.269</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>944959.6</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>1162575.356</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>1244363.792</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>1393024.021</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>1389941.183</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>1536396.459</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>1644821.873</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>218668.892</t>
+          <t>2634597316590.8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-684162.367</t>
+          <t>1019746310251.64</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-708744.779</t>
+          <t>1064797621977.38</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-707456.424</t>
+          <t>1035151478574.62</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-690146.528</t>
+          <t>1051467512959.6</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-716886.671</t>
+          <t>1101616011505.04</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-769972.613</t>
+          <t>1204665532739.9</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-764221.541</t>
+          <t>1193445526368.86</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-750088.931</t>
+          <t>1196225026222.03</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-763188.242</t>
+          <t>1257792269878.75</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-769075.409</t>
+          <t>1262728333192.4</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>-767338.005</t>
+          <t>1258910817068.14</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>-753850.91</t>
+          <t>1237120945813.79</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>-755363.919</t>
+          <t>1298761923113.03</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-756265.84</t>
+          <t>1304083180779.16</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>-757918.461</t>
+          <t>1309255860346.24</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>-757676.757</t>
+          <t>1302500855625.83</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>-764052.369</t>
+          <t>1299785806753.11</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>-768659.287</t>
+          <t>1254690449144.01</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>76833.768</t>
+          <t>1212840061702.31</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>90370.628</t>
+          <t>1289196514957.73</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>120510.651</t>
+          <t>1551072342662.37</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>133172.236</t>
+          <t>1654594560626.66</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>148406.821</t>
+          <t>1859513441470.03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>153042.666</t>
+          <t>1809949072968.38</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>166013.739</t>
+          <t>2021048017159.93</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>174456.364</t>
+          <t>2169285680541.81</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>956882244642.34</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>388686069464.542</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>385597089715.633</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>419429362672.206</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>431805008083.28</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>433143217624.679</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>464120372037.605</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>456129939563.79</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>436660126357.937</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>500190227850.466</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>492846134947.43</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>472381085881.78</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>477785197483.266</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>455607922425.081</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>469003519274.958</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>439134980478.923</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>435301201921.312</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>409252916742.601</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>388172173554.958</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>437540653396.04</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>469064928585.469</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>561746091243.924</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>597662642900.567</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>628149987256.694</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>623070105670.614</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>721022005155.556</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>775790923836.605</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>961044765.25144</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>199293404.665461</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>182798508.9904</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>154286575.064306</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>148849219.54679</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>133148731.181969</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>142504661.039062</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>136670153.01638</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>147714221.755609</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>128277611.297083</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>121273365.495943</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>103345690.614374</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>91310522.838214</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>94517575.0305034</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>84850714.1672968</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>63429779.0635158</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>59062842.1546688</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>55192736.6499202</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>56429876.1620894</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>116612236.579687</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>112031437.53992</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>109265315.903847</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>104435291.039546</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>131322950.394939</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>110416351.385834</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>115334348.590147</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>108501575.458847</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6737554.09364913</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>5525601.31718384</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>6089409.78684063</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>6243793.23060849</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>6558958.53465649</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>8015620.99042488</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8585332.05569097</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>8193187.5280138</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>7281669.21520108</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>7384555.41781377</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>7868524.31571451</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>8350011.43695771</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>8579755.11927454</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>8627492.50706898</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>8631571.2818542</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>9950027.29498779</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>10226987.5200434</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>11334897.52207</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>11105061.9769624</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>11488922.6292236</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>13589675.7829033</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>15147248.5160048</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>17149018.6415169</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18651537.7492462</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>19655211.0238383</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>20752660.5659683</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>21779631.1042623</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>9820731.91670884</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7749126.07144752</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8812929.57327268</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8808042.87886911</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>9437230.95032556</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>11819032.7024544</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>12977562.4031927</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>12462718.0646424</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>11475125.3626947</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>11791075.2601386</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>12690131.5644228</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>13533681.4217062</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>13778944.4125429</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>14535106.4380011</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>14625487.3140413</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>16933077.0282907</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>17537276.2973837</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>19316570.6497139</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>18214315.2139306</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>18224424.4393874</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>21883011.335854</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>23997319.2269399</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>27064353.2154044</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>29581985.3404169</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>30678402.8262158</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>32588301.8866189</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>34341224.4011638</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-0.771477740749012</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-2.76019266124764</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-2.8380449383656</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-2.6867117254102</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-2.59828282460887</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-2.6550799870099</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-2.65899335471864</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-2.67544700470701</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-2.71778663936113</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-2.52579598621803</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-2.56047771194004</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-2.62440459183032</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-2.57780298337323</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-2.65792533847798</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-2.61249502171871</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-2.72593506482478</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-2.74058043868402</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>-2.86694422383346</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-2.9802019293653</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>-0.824396277156617</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>-0.807338766822576</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>-0.785471314155885</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>-0.777178249389625</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>-0.763739832145878</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>-0.754373280181339</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>-0.769752188735132</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>-0.775124510673394</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>11320.4574178701</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>13887.5971653307</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>13800.4040554603</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>14852.3145423023</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>15330.718173692</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>15407.7695512545</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>16600.628515488</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>16413.4559036627</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>16050.1406439717</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>18525.5639944626</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>18637.3519494657</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>17853.6608607708</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>16747.9974861479</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>15944.2842494024</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>16399.1258273956</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>15326.5570687301</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>15202.9393638355</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>14183.330736733</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>13381.0023562616</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>13969.0487939911</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>13064.9380944519</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>11389.3457550762</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>11497.847057004</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10813.6963152219</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>10492.0524986267</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11157.6803596809</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>11363.3522069243</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>-103884724645.868</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>-45740164756.0856</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>-48155374469.3354</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-45260847026.536</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>-45762616008.1154</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>-55247484257.5801</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>-55748386071.5629</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>-61471438876.0506</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>-64711962837.6506</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>-65464274831.4142</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>-67277226230.5021</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-72487129916.1269</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-70075726158.8749</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>-86648659153.9894</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>-66222760868.0474</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.599</t>
+          <t>-70542803331.5249</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>-77712241331.7448</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-86166864214.7565</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>-97997241783.5863</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>-63977421012.1573</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.911</t>
+          <t>-52859591833.4332</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.975</t>
+          <t>-64333820440.9671</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>1.094</t>
+          <t>-81530346137.0949</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.048</t>
+          <t>-115220956389.117</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>-86735088023.0107</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>1.278</t>
+          <t>-96505657289.8605</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>-92488520298.5619</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-101685802672.638</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-45252827108.3638</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-47676714926.9517</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-44829011968.7187</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-45431259432.7613</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-54780088540.4465</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-54870024392.7007</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-60120081487.0587</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-63513118951.8818</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-63905036300.4424</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>-66233753863.7178</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-72312589979.9818</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>-70053510186.3152</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>-86422347870.5801</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>-65744214065.7678</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>-70830987429.2454</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>-77102544550.5251</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>-85497852872.3146</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>-97393277198.6283</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>-63619844515.9764</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-52577083432.2097</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>-63908651326.9986</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>-79742251777.9626</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>-113455415245.101</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>-85344951855.7182</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>-94811800176.1755</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>-92399363670.2834</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-2198921973.22966</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-487337647.721748</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-478659542.383651</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-431835057.817244</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-331356575.354165</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-467395717.133551</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-878361678.862194</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-1351357388.99193</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-1198843885.76885</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-1559238530.9718</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-1043472366.78432</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-174539936.145046</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-22215972.5596905</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-226311283.409336</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-478546802.279559</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>288184097.720513</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-609696781.219652</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-669011342.441861</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-603964584.958053</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-357576496.180913</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-282508401.223576</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-425169113.968503</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-1788094359.1323</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-1765541144.0166</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-1390136167.29249</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-1693857113.68505</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-89156628.2785506</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.487</t>
+          <t>2586.97650488628</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>-24444.8466127786</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.665</t>
+          <t>-25365.7628215389</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>-25051.5730879817</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.761</t>
+          <t>-24502.823545931</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.926</t>
+          <t>-25501.0910287418</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>-27540.3323913474</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.001</t>
+          <t>-27499.8755306823</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.989</t>
+          <t>-27570.7171580817</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.101</t>
+          <t>-28266.2311851763</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.299</t>
+          <t>-29083.1723267235</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>-29001.5686832174</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.733</t>
+          <t>-26425.0403991714</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.778</t>
+          <t>-26434.4328609796</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.935</t>
+          <t>-26443.5087572141</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2.607</t>
+          <t>-26452.6422679594</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2.875</t>
+          <t>-26461.9388671914</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>3.067</t>
+          <t>-26479.4873936632</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2.879</t>
+          <t>-26497.0866827109</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>3.054</t>
+          <t>2453.01697280571</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>3.764</t>
+          <t>2517.10708466381</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>2443.34137746074</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>4.522</t>
+          <t>2561.97040949198</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>4.572</t>
+          <t>2554.84570655784</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>2577.12843940286</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>5.322</t>
+          <t>2569.03148160954</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>5.747</t>
+          <t>2555.33938792268</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>2402.49042311727</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>2380.24793306698</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>2432.02118307424</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2406.32824374782</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>2421.00637764654</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>2399.83049514618</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>2455.51141568541</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>2421.21233267074</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>2393.38191185046</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>2417.19203255055</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>2444.75542282549</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>2408.7773771103</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>2393.53233785499</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>2394.23343217288</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>2394.93451613152</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.599</t>
+          <t>2395.63558278904</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>2396.33669315614</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>2397.69091192079</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>2399.04510789892</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>2396.8295407892</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.911</t>
+          <t>2400.67910337535</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.975</t>
+          <t>2401.48820513276</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>1.094</t>
+          <t>2400.71931616614</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1.048</t>
+          <t>2400.4053170015</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>2401.97808064066</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>1.278</t>
+          <t>2401.43790093035</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2401.49243721541</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>34815.2464977549</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>38585.0607690312</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>47700.8802397541</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>50931.648453769</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>58621.8525409179</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>81279.8474423193</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>84521.351758527</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>95135.94777022</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>95720.0899312365</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>119909.266057396</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>154255.597510991</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>195379.159801394</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>209799.598653086</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>240898.662759409</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>227422.314263937</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>337006.88179359</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>397624.537327122</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>432901.608724094</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>450541.291936803</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>427204.252403276</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>471986.077103017</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>484721.633864646</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>525032.751630142</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>571823.030291024</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>562273.962917976</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>592139.198484582</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>631158.378994251</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>153468652251.532</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>56720713159.8598</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>62138120949.4638</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>61499035214.4227</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>63814976193.0788</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>75162512840.2244</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>76797504283.3903</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>86098866528.9019</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>86767854293.8157</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>95307146987.7341</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>101162920112.106</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>107045371689.429</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>99575873963.5686</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>124021701135.939</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>103575330664.659</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>113885596739.668</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>128032445828.048</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>135666560971.732</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>155070175030.985</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>125281511152.681</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>117768569286.843</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>133445577033.891</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>153876452583.567</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>194229263116.357</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>157542701689.871</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>177017179034.135</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>174037173357.704</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>39182.7919633189</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>43316.4654183495</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>53695.2293222788</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>59243.3547245116</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>69130.2742512083</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>87329.9290782386</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>90724.0766736844</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>102076.550744593</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>100514.610099609</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>132830.906044002</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>178096.184371412</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>226976.189708812</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>255701.994839299</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>298981.947767279</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>294375.429872509</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>409594.192500271</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>512325.24651086</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>561892.711117102</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>507429.667557036</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>487360.484550397</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>530543.328840362</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>532623.351569929</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>620239.484301496</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>686723.394455463</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>647967.107821693</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>700730.396232066</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>753489.620169601</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2171833.039</t>
+          <t>52058256714.9822</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>818402.313</t>
+          <t>11941676712.4001</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>844057.515</t>
+          <t>15104815000.9059</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>843181.748</t>
+          <t>17804099690.0042</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>824584.604</t>
+          <t>19980065971.2744</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>851441.141</t>
+          <t>20853641746.893</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>906000.225</t>
+          <t>22049487412.4484</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>899003.887</t>
+          <t>25788823392.8857</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>880933.995</t>
+          <t>22870373309.2557</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>894204.418</t>
+          <t>32212569667.3179</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>897202.015</t>
+          <t>37873045964.4629</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>896040.133</t>
+          <t>39259617555.353</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>892578.846</t>
+          <t>35200417713.2867</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>894320.887</t>
+          <t>45332737573.1816</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>895341</t>
+          <t>47207493285.8829</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>897249.373</t>
+          <t>52292955182.2236</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>896914.317</t>
+          <t>63547003410.0727</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>904368.491</t>
+          <t>63563755509.226</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>909727.741</t>
+          <t>63589699015.7301</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>895207.269</t>
+          <t>67699064122.1071</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>944959.6</t>
+          <t>70569407364.9549</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>1162575.356</t>
+          <t>74192046637.1837</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>1244363.792</t>
+          <t>81516681424.5346</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>1393024.021</t>
+          <t>90428220158.6341</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>1389941.183</t>
+          <t>78628604722.5664</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>1536396.459</t>
+          <t>91049355612.0049</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>1644821.873</t>
+          <t>93468006593.8525</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>218668.892</t>
+          <t>-4367.54546556407</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-684162.367</t>
+          <t>-4731.40464931832</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-708744.779</t>
+          <t>-5994.34908252475</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-707456.424</t>
+          <t>-8311.70627074256</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-690146.528</t>
+          <t>-10508.4217102903</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-716886.671</t>
+          <t>-6050.08163591931</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-769972.613</t>
+          <t>-6202.72491515742</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-764221.541</t>
+          <t>-6940.60297437334</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>-750088.931</t>
+          <t>-4794.52016837268</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-763188.242</t>
+          <t>-12921.6399866064</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>-769075.409</t>
+          <t>-23840.586860421</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>-767338.005</t>
+          <t>-31597.0299074187</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>-753850.91</t>
+          <t>-45902.3961862128</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>-755363.919</t>
+          <t>-58083.28500787</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>-756265.84</t>
+          <t>-66953.1156085721</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>-757918.461</t>
+          <t>-72587.3107066808</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>-757676.757</t>
+          <t>-114700.709183738</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>-764052.369</t>
+          <t>-128991.102393008</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>-768659.287</t>
+          <t>-56888.3756202325</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>76833.768</t>
+          <t>-60156.2321471211</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>90370.628</t>
+          <t>-58557.251737345</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>120510.651</t>
+          <t>-47901.7177052829</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>133172.236</t>
+          <t>-95206.7326713537</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>148406.821</t>
+          <t>-114900.364164439</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>153042.666</t>
+          <t>-85693.1449037172</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>166013.739</t>
+          <t>-108591.197747484</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>174456.364</t>
+          <t>-122331.24117535</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2692249.915</t>
+          <t>101410395536.55</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1040510.694</t>
+          <t>44779036447.4598</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1086631.31</t>
+          <t>47033305948.5578</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1055400.467</t>
+          <t>43694935524.4185</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1071488.144</t>
+          <t>43834910221.8044</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1123254.871</t>
+          <t>54308871093.3314</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1229400.792</t>
+          <t>54748016870.942</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1216559.451</t>
+          <t>60310043136.0162</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1220882.235</t>
+          <t>63897480984.56</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1282269.268</t>
+          <t>63094577320.4162</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1286350.813</t>
+          <t>63289874147.6432</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1282708.353</t>
+          <t>67785754134.0765</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1261298.451</t>
+          <t>64375456250.282</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1322682.1</t>
+          <t>78688963562.7572</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1327988.954</t>
+          <t>56367837378.776</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1332862.127</t>
+          <t>61592641557.4448</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1323609.394</t>
+          <t>64485442417.9758</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1320611.76</t>
+          <t>72102805462.5057</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>1272776.675</t>
+          <t>91480476015.2552</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1230531.095</t>
+          <t>57582447030.5742</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>1308175.458</t>
+          <t>47199161921.8885</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>1576787.671</t>
+          <t>59253530396.7076</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>1682391.918</t>
+          <t>72359771159.0324</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>1889802.486</t>
+          <t>103801042957.723</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1840962.431</t>
+          <t>78914096967.3048</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2054418.208</t>
+          <t>85967823422.1303</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2204969.305</t>
+          <t>80569166763.8519</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>8.728</t>
+          <t>151868.839672323</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6.743</t>
+          <t>158147.065741227</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>186959.788277499</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>7.779</t>
+          <t>199548.832479588</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>8.342</t>
+          <t>222056.809183149</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>10.459</t>
+          <t>270724.02847927</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>11.507</t>
+          <t>287183.35354438</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>11.056</t>
+          <t>281345.5214604</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>10.216</t>
+          <t>284679.029482978</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>10.518</t>
+          <t>302734.36062113</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>11.279</t>
+          <t>352452.212138575</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>12.059</t>
+          <t>407142.253458879</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>12.237</t>
+          <t>470027.9751884</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>462286.504813229</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>13.002</t>
+          <t>496379.881372597</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>15.024</t>
+          <t>665528.619735489</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>15.55</t>
+          <t>711774.121112587</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>17.121</t>
+          <t>759917.827549337</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>16.042</t>
+          <t>769567.787377216</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>15.931</t>
+          <t>804912.613323103</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>18.912</t>
+          <t>1008864.71920706</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>20.688</t>
+          <t>1086034.25771591</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>23.157</t>
+          <t>1213261.35762949</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>25.281</t>
+          <t>1223944.59893119</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>26.051</t>
+          <t>1336922.27737803</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>27.692</t>
+          <t>1423782.54895506</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>29.166</t>
+          <t>1553166.3383713</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1807476.478</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>727141.552</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>735735.944</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>733792.045</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>730779.172</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>747111.599</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>796948.864</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>784589.923</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>759077.977</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>787734.495</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>782955.523</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>776722.859</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>770319.877</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>770896.23</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>769635</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>769330.437</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>759562.646</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>762709.861</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>764970.576</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>764590.71</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>800610.226</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>979045.952</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>1048414.966</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>1172429.259</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>1159608.314</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>1287030.04</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>1375787.926</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>165890.380114723</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4.712</t>
+          <t>181566.639091862</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>209923.175376243</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>5.409</t>
+          <t>225755.190750702</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>5.689</t>
+          <t>260676.09661058</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6.957</t>
+          <t>316344.332719934</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>7.459</t>
+          <t>341481.457521538</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>336420.234393454</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>6.352</t>
+          <t>330774.073212742</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>6.461</t>
+          <t>361352.565961257</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>6.865</t>
+          <t>421149.811703597</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>7.302</t>
+          <t>477662.524872948</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>7.474</t>
+          <t>557942.716026678</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>7.582</t>
+          <t>553910.147966076</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>7.535</t>
+          <t>598548.268723215</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>8.672</t>
+          <t>795567.444156713</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>8.923</t>
+          <t>845887.769296598</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>9.888</t>
+          <t>917077.057902683</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>9.641</t>
+          <t>888891.742074571</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>9.899</t>
+          <t>958877.703613374</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>11.574</t>
+          <t>1210312.89356889</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>12.846</t>
+          <t>1295405.20036971</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>14.431</t>
+          <t>1452887.6595706</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15.684</t>
+          <t>1391925.11548332</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>16.409</t>
+          <t>1494082.63864455</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17.348</t>
+          <t>1697719.11932195</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>18.198</t>
+          <t>1859751.85008617</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>955790.142</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>389606.967</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>386480.181</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>419964.887</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>432250.882</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>433783.337</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>465208.867</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>456867.403</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>438027.184</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>501256.555</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>493655.839</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>473103.076</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>478877.611</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>456038.152</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>469208.271</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>438766.42</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>434209.464</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>407888.851</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>386735.912</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>434753.705</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>466472.929</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>559129.552</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>594921.767</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>625073.416</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>621300.704</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>718561.134</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>773631.583</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>-77.12</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-275.6</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-283.38</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-268.46</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-259.66</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-265.26</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-265.51</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-267.27</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-271.24</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-252.26</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-255.79</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-262.19</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>-257.42</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>-265.64</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>-261.18</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>-272.74</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>-274.5</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>-287.32</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>-298.76</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>-82.33</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>-80.63</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>-78.45</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>-77.62</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>-76.26</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>-75.37</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>-76.9</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>-77.45</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1282.517</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>266.032</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>244.009</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>205.857</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>198.481</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>177.458</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>190.035</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>182.24</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>196.995</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>171.062</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>161.531</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>137.693</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>121.628</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>125.855</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>112.975</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>84.435</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>78.53</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>73.4</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>74.993</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>154.827</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>148.727</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>145.188</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>138.766</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>174.466</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>146.713</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>153.231</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>144.164</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>166848.072262418</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>183985.377777544</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>228802.050526806</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>225885.985146204</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>249842.471482944</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>291472.749297602</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>306715.574768333</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>302105.263202065</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>292328.719298025</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>306028.413066079</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>357655.721318099</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>396210.489432738</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>459001.054942688</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>457914.042381664</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>510909.23845095</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>676034.033988918</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>711066.426197398</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>768591.013933059</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>768351.189348776</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>823137.6657039</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>1037212.2724192</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>1095989.84542869</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>1230380.9276029</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>1280427.24657067</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>1428886.76409304</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>1498781.84603606</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>1567894.62428782</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>218668892382.824</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>-684162367000.679</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-708744779000.323</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-707456424000.536</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-690146527999.599</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-716886670999.68</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-769972612999.931</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>-764221540999.341</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>-750088930999.408</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-763188241999.723</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>-769075409001.259</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>-767338005000.157</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>-753850910000.665</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>-755363918999.853</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>-756265839999.424</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>-757918460999.716</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>-757676756999.878</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>-764052368999.593</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>-768659286999.45</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>76833767631.6711</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>90370627581.5568</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>120510650732.627</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>133172236365.528</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>148406821426.831</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>153042666272.94</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>166013738560.873</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>174456363612.896</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2171833039490.27</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>818402313000.033</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>844057515000.015</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>843181748000.152</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>824584604000.182</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>851441140999.95</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>906000224999.802</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>899003886999.949</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>880933995000.16</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>894204418000.016</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>897202014999.877</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>896040133000.049</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>892578845999.921</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>894320886999.811</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>895340999999.962</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>897249373000.143</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>896914317000.024</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>904368491000.193</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>909727741000.242</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>895207269406.163</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>944959599879.792</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>1162575356154.66</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>1244363792448.83</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>1393024021254.7</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>1389941183177.29</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>1536396458761.45</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>1644821873447.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1807476477930.58</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>727141551597.863</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>735735944144.833</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>733792044778.106</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>730779171808.067</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>747111599359.071</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>796948863992.633</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>784589922622.928</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>759077977153.23</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>787734495463.498</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>782955522834.875</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>776722858554.144</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>770319877213.935</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>770896230304.119</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>769635000233.856</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>769330436801.472</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>759562646413.821</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>762709861256.132</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>764970575945.151</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>764590710497.577</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>800610226345.74</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>979045951692.52</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>1048414966302.94</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>1172429258878.14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>1159608313806.8</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>1287030040214.07</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>1375787925615.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>903992381.652153</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>343830700.000025</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>347060100.000062</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>350401800.000031</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>340595800.00023</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>354792199.999978</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>368966000.000008</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>371303199.999934</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>368070799.999929</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>369935200.000009</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>366990499.999771</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>371989599.999891</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>372912799.999946</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>373531200.000065</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>373847800.000054</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>374535000.000104</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>374285600.000025</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>377183100.000033</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>379204100.000013</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>373496426.913781</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>393621787.498038</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>484106211.169331</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>518329562.339685</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>580328668.407889</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>578665223.625424</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>639781881.582791</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>684916532.718532</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>84526818.0711355</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>27988000.0000913</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>27941000.0001461</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>28239999.9998376</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>28166000.0002002</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>28111999.9999879</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>27958000.0000959</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>27790000.0000611</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>27205999.999878</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>26999999.9999987</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>26443999.9997725</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>26458499.9998362</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>28527899.9998918</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>28574999.9999002</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>28599299.9999709</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>28651900.0000897</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>28632699.999896</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>28854499.9999675</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>29009200.0001266</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>31322150.8385204</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>35902575.6719552</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>49322068.477336</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>51980395.9765228</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>58088369.5034487</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>59384958.8297588</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>64621138.2574661</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>68271308.475669</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2171833039490.27</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>818402313000.033</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>844057515000.015</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>843181748000.152</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>824584604000.182</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>851441140999.95</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>906000224999.802</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>899003886999.949</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>880933995000.16</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>894204418000.016</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>897202014999.877</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>896040133000.049</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>892578845999.921</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>894320886999.811</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>895340999999.962</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>897249373000.143</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>896914317000.024</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>904368491000.193</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>909727741000.242</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>895207269406.163</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>944959599879.792</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>1162575356154.66</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>1244363792448.83</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>1393024021254.7</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>1389941183177.29</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>1536396458761.45</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>1644821873447.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>218668892382.824</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>-684162367000.679</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-708744779000.323</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-707456424000.536</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-690146527999.599</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-716886670999.68</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>-769972612999.931</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>-764221540999.341</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>-750088930999.408</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>-763188241999.723</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>-769075409001.259</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>-767338005000.157</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>-753850910000.665</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>-755363918999.853</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>-756265839999.424</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>-757918460999.716</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>-757676756999.878</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>-764052368999.593</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>-768659286999.45</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>76833767631.6711</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>90370627581.5568</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>120510650732.627</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>133172236365.528</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>148406821426.831</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>153042666272.94</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>166013738560.873</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>174456363612.896</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>646782.677082662</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>714849.079738505</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>883834.867966698</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>887407.530343927</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1011459.62226251</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1229542.67998627</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1301096.04390797</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1329874.91854735</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1313609.44647064</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1462468.4118203</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1725530.31797891</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1999727.19612898</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2302165.75374839</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2361244.85933732</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2570567.97933004</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>3462575.38642759</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>3818308.4059168</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>4074001.44393014</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>3823915.25598933</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>4057183.23832861</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>5000494.2737369</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>5339290.98713046</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>6006493.69944028</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>6073012.39830422</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>6628073.55596922</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>7069329.8866738</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>7633356.45153151</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>210712.333724318</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>227837.51441964</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>269668.913841382</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>283068.627648492</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>325703.731342495</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>393335.65828407</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>421028.58395745</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>418225.354950057</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>411619.747339733</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>444842.132317808</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>521736.900990508</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>597273.20251814</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>689298.106816933</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>686813.969257674</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>741678.602342143</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>996938.026146487</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1075277.24227945</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1155387.21476827</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1149089.07974069</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1219601.24039577</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>1533038.71617379</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>1652901.13823071</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>1856953.79154826</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>1839348.06357765</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2002194.06175588</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>2173609.80899672</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>2377787.86076033</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
